--- a/docs/Federated_RAG_Privacy.xlsx
+++ b/docs/Federated_RAG_Privacy.xlsx
@@ -14,8 +14,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="31">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000E+00"/>
+  </numFmts>
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -178,6 +180,22 @@
       <name val="Calibri"/>
       <color rgb="009C6500"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="15">
@@ -399,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -620,6 +638,18 @@
     <xf numFmtId="0" fontId="18" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -693,6 +723,367 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Test Hit@1 theo ε  (DP giữ = pretrained toàn dải)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Khung 1 — Chi tiết'!B49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Khung 1 — Chi tiết'!$A$50:$A$53</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Khung 1 — Chi tiết'!$B$50:$B$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Khung 1 — Chi tiết'!C49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Khung 1 — Chi tiết'!$A$50:$A$53</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Khung 1 — Chi tiết'!$C$50:$C$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Khung 1 — Chi tiết'!D49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Khung 1 — Chi tiết'!$A$50:$A$53</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Khung 1 — Chi tiết'!$D$50:$D$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>ε (privacy budget)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="80"/>
+          <min val="40"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Test Hit@1 (%)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="3"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>lora_B std theo ε  (trọng số nhích nhẹ, luôn &lt; ngưỡng học 1e-3)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Khung 1 — Chi tiết'!E49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="diamond"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Khung 1 — Chi tiết'!$A$50:$A$53</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Khung 1 — Chi tiết'!$E$50:$E$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>ε (privacy budget)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>lora_B std</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5894,7 +6285,6 @@
   <mergeCells count="16">
     <mergeCell ref="W1:W2"/>
     <mergeCell ref="X1:X2"/>
-    <mergeCell ref="Q1:S1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="C1:C2"/>
@@ -5903,10 +6293,11 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="I1:I2"/>
+    <mergeCell ref="Q1:S1"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="N1:P1"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="H1:H2"/>
+    <mergeCell ref="N1:P1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>
   <dataValidations count="2">
@@ -9288,7 +9679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="49" min="1" max="1"/>
@@ -9306,12 +9697,12 @@
           <t>KHUNG ĐÁNH GIÁ SỐ 1 — Hiệu quả Retriever sau Federated Training &amp; Đánh đổi Privacy–Utility</t>
         </is>
       </c>
-      <c r="B1" s="54" t="n"/>
-      <c r="C1" s="54" t="n"/>
-      <c r="D1" s="54" t="n"/>
-      <c r="E1" s="54" t="n"/>
-      <c r="F1" s="54" t="n"/>
-      <c r="G1" s="54" t="n"/>
+      <c r="B1" s="61" t="n"/>
+      <c r="C1" s="61" t="n"/>
+      <c r="D1" s="61" t="n"/>
+      <c r="E1" s="61" t="n"/>
+      <c r="F1" s="61" t="n"/>
+      <c r="G1" s="60" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="55" t="inlineStr">
@@ -9319,12 +9710,12 @@
           <t>Nguồn dữ liệu: FedE4RAG (Mao et al., 2025) · bộ tài chính 5 công ty · paper-protocol eval · cập nhật từ bảng tổng hợp 11 training-runs của nhóm</t>
         </is>
       </c>
-      <c r="B2" s="54" t="n"/>
-      <c r="C2" s="54" t="n"/>
-      <c r="D2" s="54" t="n"/>
-      <c r="E2" s="54" t="n"/>
-      <c r="F2" s="54" t="n"/>
-      <c r="G2" s="54" t="n"/>
+      <c r="B2" s="61" t="n"/>
+      <c r="C2" s="61" t="n"/>
+      <c r="D2" s="61" t="n"/>
+      <c r="E2" s="61" t="n"/>
+      <c r="F2" s="61" t="n"/>
+      <c r="G2" s="60" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="56" t="inlineStr">
@@ -9332,12 +9723,12 @@
           <t>1 · MỤC TIÊU</t>
         </is>
       </c>
-      <c r="B4" s="54" t="n"/>
-      <c r="C4" s="54" t="n"/>
-      <c r="D4" s="54" t="n"/>
-      <c r="E4" s="54" t="n"/>
-      <c r="F4" s="54" t="n"/>
-      <c r="G4" s="54" t="n"/>
+      <c r="B4" s="61" t="n"/>
+      <c r="C4" s="61" t="n"/>
+      <c r="D4" s="61" t="n"/>
+      <c r="E4" s="61" t="n"/>
+      <c r="F4" s="61" t="n"/>
+      <c r="G4" s="60" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1" s="49">
       <c r="A5" s="57" t="inlineStr">
@@ -9345,12 +9736,12 @@
           <t>Đo độ hiệu quả của bộ retriever (embedding model) sau khi train federated, nhằm cải thiện độ chính xác tìm tài liệu liên quan tới query; và ĐỊNH LƯỢNG cái giá phải trả về độ chính xác khi thêm các cơ chế bảo mật (Differential Privacy + LoRA thay cho full fine-tuning của paper gốc).</t>
         </is>
       </c>
-      <c r="B5" s="54" t="n"/>
-      <c r="C5" s="54" t="n"/>
-      <c r="D5" s="54" t="n"/>
-      <c r="E5" s="54" t="n"/>
-      <c r="F5" s="54" t="n"/>
-      <c r="G5" s="54" t="n"/>
+      <c r="B5" s="61" t="n"/>
+      <c r="C5" s="61" t="n"/>
+      <c r="D5" s="61" t="n"/>
+      <c r="E5" s="61" t="n"/>
+      <c r="F5" s="61" t="n"/>
+      <c r="G5" s="60" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="56" t="inlineStr">
@@ -9358,12 +9749,12 @@
           <t>2 · DATASET</t>
         </is>
       </c>
-      <c r="B7" s="54" t="n"/>
-      <c r="C7" s="54" t="n"/>
-      <c r="D7" s="54" t="n"/>
-      <c r="E7" s="54" t="n"/>
-      <c r="F7" s="54" t="n"/>
-      <c r="G7" s="54" t="n"/>
+      <c r="B7" s="61" t="n"/>
+      <c r="C7" s="61" t="n"/>
+      <c r="D7" s="61" t="n"/>
+      <c r="E7" s="61" t="n"/>
+      <c r="F7" s="61" t="n"/>
+      <c r="G7" s="60" t="n"/>
     </row>
     <row r="8" ht="70" customHeight="1" s="49">
       <c r="A8" s="57" t="inlineStr">
@@ -9373,12 +9764,12 @@
 • Split đánh giá: val = 50 cặp, test = 100 cặp (đúng bộ val/test của paper gốc → so sánh công bằng vì chung cốt lõi kiến trúc; chỉ khác cách triển khai security).</t>
         </is>
       </c>
-      <c r="B8" s="54" t="n"/>
-      <c r="C8" s="54" t="n"/>
-      <c r="D8" s="54" t="n"/>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="54" t="n"/>
-      <c r="G8" s="54" t="n"/>
+      <c r="B8" s="61" t="n"/>
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="61" t="n"/>
+      <c r="E8" s="61" t="n"/>
+      <c r="F8" s="61" t="n"/>
+      <c r="G8" s="60" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="56" t="inlineStr">
@@ -9386,12 +9777,12 @@
           <t>3 · GIAO THỨC ĐÁNH GIÁ  (eval protocol — BẮT BUỘC ghi rõ để so sánh đúng chuẩn)</t>
         </is>
       </c>
-      <c r="B10" s="54" t="n"/>
-      <c r="C10" s="54" t="n"/>
-      <c r="D10" s="54" t="n"/>
-      <c r="E10" s="54" t="n"/>
-      <c r="F10" s="54" t="n"/>
-      <c r="G10" s="54" t="n"/>
+      <c r="B10" s="61" t="n"/>
+      <c r="C10" s="61" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="E10" s="61" t="n"/>
+      <c r="F10" s="61" t="n"/>
+      <c r="G10" s="60" t="n"/>
     </row>
     <row r="11" ht="104" customHeight="1" s="49">
       <c r="A11" s="58" t="inlineStr">
@@ -9404,12 +9795,12 @@
 → Vì vậy việc so với "Paper claim 87" CHỈ hợp lệ khi cùng paper-protocol; phần lớn khoảng cách là do GIAO THỨC ĐO.</t>
         </is>
       </c>
-      <c r="B11" s="54" t="n"/>
-      <c r="C11" s="54" t="n"/>
-      <c r="D11" s="54" t="n"/>
-      <c r="E11" s="54" t="n"/>
-      <c r="F11" s="54" t="n"/>
-      <c r="G11" s="54" t="n"/>
+      <c r="B11" s="61" t="n"/>
+      <c r="C11" s="61" t="n"/>
+      <c r="D11" s="61" t="n"/>
+      <c r="E11" s="61" t="n"/>
+      <c r="F11" s="61" t="n"/>
+      <c r="G11" s="60" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="56" t="inlineStr">
@@ -9417,12 +9808,12 @@
           <t>4 · BỘ CHỈ SỐ (phân tầng — tránh liệt kê dàn trải)</t>
         </is>
       </c>
-      <c r="B13" s="54" t="n"/>
-      <c r="C13" s="54" t="n"/>
-      <c r="D13" s="54" t="n"/>
-      <c r="E13" s="54" t="n"/>
-      <c r="F13" s="54" t="n"/>
-      <c r="G13" s="54" t="n"/>
+      <c r="B13" s="61" t="n"/>
+      <c r="C13" s="61" t="n"/>
+      <c r="D13" s="61" t="n"/>
+      <c r="E13" s="61" t="n"/>
+      <c r="F13" s="61" t="n"/>
+      <c r="G13" s="60" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="59" t="inlineStr">
@@ -9456,15 +9847,15 @@
           <t>Hit@1, Hit@10, MRR</t>
         </is>
       </c>
-      <c r="C15" s="63" t="n"/>
+      <c r="C15" s="60" t="n"/>
       <c r="D15" s="63" t="inlineStr">
         <is>
           <t>So TRỰC TIẾP với paper (cùng định nghĩa). Đây là số báo cáo chính.</t>
         </is>
       </c>
-      <c r="E15" s="63" t="n"/>
-      <c r="F15" s="63" t="n"/>
-      <c r="G15" s="63" t="n"/>
+      <c r="E15" s="61" t="n"/>
+      <c r="F15" s="61" t="n"/>
+      <c r="G15" s="60" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="64" t="inlineStr">
@@ -9477,15 +9868,15 @@
           <t>Recall@k, NDCG, MAP, EM</t>
         </is>
       </c>
-      <c r="C16" s="65" t="n"/>
+      <c r="C16" s="60" t="n"/>
       <c r="D16" s="65" t="inlineStr">
         <is>
           <t>Bổ trợ chất lượng ranking/độ phủ; báo cáo khi cần làm rõ.</t>
         </is>
       </c>
-      <c r="E16" s="65" t="n"/>
-      <c r="F16" s="65" t="n"/>
-      <c r="G16" s="65" t="n"/>
+      <c r="E16" s="61" t="n"/>
+      <c r="F16" s="61" t="n"/>
+      <c r="G16" s="60" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="62" t="inlineStr">
@@ -9498,15 +9889,15 @@
           <t>ε spent, lora_B std</t>
         </is>
       </c>
-      <c r="C17" s="63" t="n"/>
+      <c r="C17" s="60" t="n"/>
       <c r="D17" s="63" t="inlineStr">
         <is>
           <t>Kiểm chứng privacy (ε ≤ target) + model CÓ THỰC SỰ HỌC không.</t>
         </is>
       </c>
-      <c r="E17" s="63" t="n"/>
-      <c r="F17" s="63" t="n"/>
-      <c r="G17" s="63" t="n"/>
+      <c r="E17" s="61" t="n"/>
+      <c r="F17" s="61" t="n"/>
+      <c r="G17" s="60" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="56" t="inlineStr">
@@ -9514,12 +9905,12 @@
           <t>5 · KẾT QUẢ — KHỐI A: biến thể TRAINING  (trả lời trực tiếp câu hỏi đánh đổi DP/LoRA)</t>
         </is>
       </c>
-      <c r="B19" s="54" t="n"/>
-      <c r="C19" s="54" t="n"/>
-      <c r="D19" s="54" t="n"/>
-      <c r="E19" s="54" t="n"/>
-      <c r="F19" s="54" t="n"/>
-      <c r="G19" s="54" t="n"/>
+      <c r="B19" s="61" t="n"/>
+      <c r="C19" s="61" t="n"/>
+      <c r="D19" s="61" t="n"/>
+      <c r="E19" s="61" t="n"/>
+      <c r="F19" s="61" t="n"/>
+      <c r="G19" s="60" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="59" t="inlineStr">
@@ -9649,12 +10040,12 @@
           <t>→ Kết luận khối A: DP KHÔNG làm giảm (≡ pretrained); ngược lại Non-DP fine-tune mới gây hại do overfit. DP &gt; Non-DP khoảng +4–6% Hit@1 trên test out-of-domain.</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="54" t="n"/>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
+      <c r="B24" s="61" t="n"/>
+      <c r="C24" s="61" t="n"/>
+      <c r="D24" s="61" t="n"/>
+      <c r="E24" s="61" t="n"/>
+      <c r="F24" s="61" t="n"/>
+      <c r="G24" s="60" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="56" t="inlineStr">
@@ -9662,12 +10053,12 @@
           <t>6 · KẾT QUẢ — KHỐI B: biến thể EVAL-SIDE  (không train, chạy trên pretrained)</t>
         </is>
       </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="54" t="n"/>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
+      <c r="B26" s="61" t="n"/>
+      <c r="C26" s="61" t="n"/>
+      <c r="D26" s="61" t="n"/>
+      <c r="E26" s="61" t="n"/>
+      <c r="F26" s="61" t="n"/>
+      <c r="G26" s="60" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="59" t="inlineStr">
@@ -9859,12 +10250,12 @@
           <t>7 · ĐƯỜNG CONG PRIVACY–UTILITY  (ε-sweep, paper-protocol + LlamaIndex)</t>
         </is>
       </c>
-      <c r="B34" s="54" t="n"/>
-      <c r="C34" s="54" t="n"/>
-      <c r="D34" s="54" t="n"/>
-      <c r="E34" s="54" t="n"/>
-      <c r="F34" s="54" t="n"/>
-      <c r="G34" s="54" t="n"/>
+      <c r="B34" s="61" t="n"/>
+      <c r="C34" s="61" t="n"/>
+      <c r="D34" s="61" t="n"/>
+      <c r="E34" s="61" t="n"/>
+      <c r="F34" s="61" t="n"/>
+      <c r="G34" s="60" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="59" t="inlineStr">
@@ -9895,30 +10286,26 @@
       <c r="F35" s="61" t="n"/>
       <c r="G35" s="60" t="n"/>
     </row>
-    <row r="36">
-      <c r="A36" s="79" t="n">
+    <row r="36" ht="44" customHeight="1" s="49">
+      <c r="A36" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="77" t="n">
+      <c r="B36" s="73" t="n">
         <v>28.13</v>
       </c>
-      <c r="C36" s="77" t="inlineStr">
-        <is>
-          <t>chờ eval</t>
-        </is>
-      </c>
-      <c r="D36" s="77" t="inlineStr">
-        <is>
-          <t>chờ eval</t>
-        </is>
-      </c>
-      <c r="E36" s="78" t="inlineStr">
-        <is>
-          <t>✅ train xong (eps_spent 0.99/1.0) · ❌ CHƯA eval</t>
-        </is>
-      </c>
-      <c r="F36" s="80" t="n"/>
-      <c r="G36" s="80" t="n"/>
+      <c r="C36" s="73" t="n">
+        <v>62</v>
+      </c>
+      <c r="D36" s="73" t="n">
+        <v>62</v>
+      </c>
+      <c r="E36" s="74" t="inlineStr">
+        <is>
+          <t>✅ ĐO THẬT (LlamaIndex): val H@1=62/H@10=68/MRR=48.47 · test H@1=62/H@10=71/MRR=46.80 = pretrained hoàn toàn. lora_B std=2.47e-04. Invariance xác nhận ở privacy mạnh nhất.</t>
+        </is>
+      </c>
+      <c r="F36" s="61" t="n"/>
+      <c r="G36" s="60" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="81" t="n">
@@ -9938,71 +10325,63 @@
           <t>✅ XONG — = pretrained (đã có checkpoint + eval)</t>
         </is>
       </c>
-      <c r="F37" s="82" t="n"/>
-      <c r="G37" s="82" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="79" t="n">
+      <c r="F37" s="61" t="n"/>
+      <c r="G37" s="60" t="n"/>
+    </row>
+    <row r="38" ht="30" customHeight="1" s="49">
+      <c r="A38" s="81" t="n">
         <v>50</v>
       </c>
-      <c r="B38" s="77" t="n">
+      <c r="B38" s="73" t="n">
         <v>1.05</v>
       </c>
-      <c r="C38" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D38" s="77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="78" t="inlineStr">
-        <is>
-          <t>⚠ DỞ — dừng ở round ~30/50, phải train lại</t>
-        </is>
-      </c>
-      <c r="F38" s="80" t="n"/>
-      <c r="G38" s="80" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="83" t="n">
+      <c r="C38" s="73" t="n">
+        <v>62</v>
+      </c>
+      <c r="D38" s="73" t="n">
+        <v>62</v>
+      </c>
+      <c r="E38" s="74" t="inlineStr">
+        <is>
+          <t>✅ ĐO THẬT: val H@1=62/MRR=48.47 · test H@1=62/MRR=46.88 = pretrained. σ=1.05 chưa phá invariance.</t>
+        </is>
+      </c>
+      <c r="F38" s="61" t="n"/>
+      <c r="G38" s="60" t="n"/>
+    </row>
+    <row r="39" ht="44" customHeight="1" s="49">
+      <c r="A39" s="81" t="n">
         <v>100</v>
       </c>
-      <c r="B39" s="70" t="n">
+      <c r="B39" s="73" t="n">
         <v>0.73</v>
       </c>
-      <c r="C39" s="70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D39" s="70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="71" t="inlineStr">
-        <is>
-          <t>❌ FAIL — server CPU bottleneck, phải train lại</t>
-        </is>
-      </c>
-      <c r="F39" s="84" t="n"/>
-      <c r="G39" s="84" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1" s="49">
+      <c r="C39" s="73" t="n">
+        <v>62</v>
+      </c>
+      <c r="D39" s="73" t="n">
+        <v>62</v>
+      </c>
+      <c r="E39" s="74" t="inlineStr">
+        <is>
+          <t>✅ ĐO THẬT: val H@1=62/MRR=48.47 · test H@1=62/MRR=47.03 = pretrained. σ=0.73 (nhiễu yếu nhất) VẪN không phá invariance → không có 'cliff' trong dải [1,100].</t>
+        </is>
+      </c>
+      <c r="F39" s="74" t="n"/>
+      <c r="G39" s="74" t="n"/>
+    </row>
+    <row r="40" ht="60" customHeight="1" s="49">
       <c r="A40" s="75" t="inlineStr">
         <is>
-          <t>→ σ càng lớn (ε nhỏ) ⇒ nhiễu áp đảo ⇒ DP ≡ pretrained (AdamW invariance). Điểm cần dữ liệu nhất: ε=100 (σ≈0.73) — kỳ vọng là ngưỡng có thể 'phá vỡ' invariance &amp; bắt đầu vượt pretrained.</t>
-        </is>
-      </c>
-      <c r="B40" s="54" t="n"/>
-      <c r="C40" s="54" t="n"/>
-      <c r="D40" s="54" t="n"/>
-      <c r="E40" s="54" t="n"/>
-      <c r="F40" s="54" t="n"/>
-      <c r="G40" s="54" t="n"/>
+          <t>✅ ε-SWEEP HOÀN TẤT (2026-07-04): Hit@1 PHẲNG ở 62 toàn dải ε∈[1,100] = pretrained → KHÔNG có 'cliff'. lora_B std tăng ĐƠN ĐIỆU theo ε (2.47→2.55→2.70→2.89 e-04 khi σ 28→0.73) — trọng số nhích dần khi nhiễu yếu đi (khớp cơ chế AdamW), nhưng LUÔN &lt; ngưỡng học 1e-3 (~6-10× thấp hơn). MRR test cũng nhích nhẹ 46.80→47.03. ⇒ Cần ε ≫ 100 mới có khả năng phá invariance.</t>
+        </is>
+      </c>
+      <c r="B40" s="61" t="n"/>
+      <c r="C40" s="61" t="n"/>
+      <c r="D40" s="61" t="n"/>
+      <c r="E40" s="61" t="n"/>
+      <c r="F40" s="61" t="n"/>
+      <c r="G40" s="60" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="56" t="inlineStr">
@@ -10010,29 +10389,30 @@
           <t>8 · KẾT LUẬN &amp; TIẾN ĐỘ  (framing chính xác — thay cho 'giảm 10–15%')</t>
         </is>
       </c>
-      <c r="B42" s="54" t="n"/>
-      <c r="C42" s="54" t="n"/>
-      <c r="D42" s="54" t="n"/>
-      <c r="E42" s="54" t="n"/>
-      <c r="F42" s="54" t="n"/>
-      <c r="G42" s="54" t="n"/>
-    </row>
-    <row r="43" ht="116" customHeight="1" s="49">
+      <c r="B42" s="61" t="n"/>
+      <c r="C42" s="61" t="n"/>
+      <c r="D42" s="61" t="n"/>
+      <c r="E42" s="61" t="n"/>
+      <c r="F42" s="61" t="n"/>
+      <c r="G42" s="60" t="n"/>
+    </row>
+    <row r="43" ht="130" customHeight="1" s="49">
       <c r="A43" s="57" t="inlineStr">
         <is>
           <t>1) DP retention ≈ 100%: DP ε=20 ≡ pretrained (bit-identical) → chi phí privacy ~0% trên giao thức paper.
 2) DP &gt; Non-DP: Non-DP fine-tune GIẢM do overfit data 5-cty; DP hơn +4–6% Hit@1 trên test out-of-domain.
-3) Khoảng cách tới 87% của paper CHỦ YẾU do KHÁC GIAO THỨC đo (append refs + Recall@K + query-expansion), không phải mất chất lượng model.
-4) lora_B std: DP = 0.000255 (gần như không dịch chuyển) vs Non-DP ≈ 0.0017 (có học) → xác nhận AdamW invariance.
-5) Caveat thống kê: n = 50/100 nhỏ; QE3 do_sample ngẫu nhiên → số dao động giữa các lần (nên báo cáo khoảng tin cậy).</t>
-        </is>
-      </c>
-      <c r="B43" s="54" t="n"/>
-      <c r="C43" s="54" t="n"/>
-      <c r="D43" s="54" t="n"/>
-      <c r="E43" s="54" t="n"/>
-      <c r="F43" s="54" t="n"/>
-      <c r="G43" s="54" t="n"/>
+3) Khoảng cách tới 87% của paper CHỦ YẾU do KHÁC GIAO THỨC đo (append refs + Recall@K + query-expansion).
+4) lora_B std: DP = 2.5e-04 vs Non-DP ≈ 1.7e-3 → xác nhận AdamW invariance.
+5) Caveat: n = 50/100 nhỏ; QE3 ngẫu nhiên → nên báo cáo khoảng tin cậy.
+6) ★ ε-SWEEP [1,100] ĐO THẬT: Hit@1 phẳng 62 toàn dải → DP 'miễn phí' bất kể ε; lora_B std chỉ nhích 2.47→2.89e-04 (luôn &lt;1e-3). Không có cliff → invariance cực bền.</t>
+        </is>
+      </c>
+      <c r="B43" s="61" t="n"/>
+      <c r="C43" s="61" t="n"/>
+      <c r="D43" s="61" t="n"/>
+      <c r="E43" s="61" t="n"/>
+      <c r="F43" s="61" t="n"/>
+      <c r="G43" s="60" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="56" t="inlineStr">
@@ -10040,31 +10420,165 @@
           <t>9 · VIỆC CÒN LẠI</t>
         </is>
       </c>
-      <c r="B45" s="54" t="n"/>
-      <c r="C45" s="54" t="n"/>
-      <c r="D45" s="54" t="n"/>
-      <c r="E45" s="54" t="n"/>
-      <c r="F45" s="54" t="n"/>
-      <c r="G45" s="54" t="n"/>
-    </row>
-    <row r="46" ht="78" customHeight="1" s="49">
+      <c r="B45" s="61" t="n"/>
+      <c r="C45" s="61" t="n"/>
+      <c r="D45" s="61" t="n"/>
+      <c r="E45" s="61" t="n"/>
+      <c r="F45" s="61" t="n"/>
+      <c r="G45" s="60" t="n"/>
+    </row>
+    <row r="46" ht="92" customHeight="1" s="49">
       <c r="A46" s="85" t="inlineStr">
         <is>
-          <t>(a) Eval checkpoint ε=1 đã train xong (≈5 phút GPU, ~$0.05) → lấp điểm dữ liệu còn trống trong bảng §7.
-(b) Train lại ε=50 + ε=100 trên server CPU ≥ 2500 MHz &amp; ≥ 16 effective cores (~4h, +$1.4) — tránh CPU bottleneck.
-(c) Hoàn tất đường cong ε &amp; vẽ biểu đồ privacy–utility (Hit@1/MRR theo ε).
-(d) (tùy chọn) bổ sung Recall@k / NDCG và bootstrap CI cho n nhỏ để tăng độ tin cậy thống kê.</t>
-        </is>
-      </c>
-      <c r="B46" s="54" t="n"/>
-      <c r="C46" s="54" t="n"/>
-      <c r="D46" s="54" t="n"/>
-      <c r="E46" s="54" t="n"/>
-      <c r="F46" s="54" t="n"/>
-      <c r="G46" s="54" t="n"/>
+          <t>✅ (a) Eval ε=1 — XONG (62/62 = pretrained).
+✅ (b) Train + eval ε=50, ε=100 — XONG trên Ryzen 5 3600 (Vast.ai), ~2h15m/ε, không bottleneck.
+✅ (c) Đường cong privacy–utility — XONG (xem §10 bên dưới).
+☐ (d) (tùy chọn) thêm Recall@k / NDCG + bootstrap CI cho n nhỏ.
+☐ (e) (tùy chọn) hình publication-quality (matplotlib PNG) cho paper.</t>
+        </is>
+      </c>
+      <c r="B46" s="61" t="n"/>
+      <c r="C46" s="61" t="n"/>
+      <c r="D46" s="61" t="n"/>
+      <c r="E46" s="61" t="n"/>
+      <c r="F46" s="61" t="n"/>
+      <c r="G46" s="60" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="56" t="inlineStr">
+        <is>
+          <t>10 · BIỂU ĐỒ PRIVACY–UTILITY (dữ liệu đo thật, paper-protocol + LlamaIndex)</t>
+        </is>
+      </c>
+      <c r="B48" s="54" t="n"/>
+      <c r="C48" s="54" t="n"/>
+      <c r="D48" s="54" t="n"/>
+      <c r="E48" s="54" t="n"/>
+      <c r="F48" s="54" t="n"/>
+      <c r="G48" s="54" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="86" t="inlineStr">
+        <is>
+          <t>ε</t>
+        </is>
+      </c>
+      <c r="B49" s="86" t="inlineStr">
+        <is>
+          <t>DP fine-tune</t>
+        </is>
+      </c>
+      <c r="C49" s="86" t="inlineStr">
+        <is>
+          <t>Non-DP (ref)</t>
+        </is>
+      </c>
+      <c r="D49" s="86" t="inlineStr">
+        <is>
+          <t>Paper claim</t>
+        </is>
+      </c>
+      <c r="E49" s="86" t="inlineStr">
+        <is>
+          <t>lora_B std</t>
+        </is>
+      </c>
+      <c r="F49" s="86" t="inlineStr">
+        <is>
+          <t>σ</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" s="87" t="n">
+        <v>62</v>
+      </c>
+      <c r="C50" s="87" t="n">
+        <v>56</v>
+      </c>
+      <c r="D50" s="87" t="n">
+        <v>73</v>
+      </c>
+      <c r="E50" s="88" t="n">
+        <v>0.0002466</v>
+      </c>
+      <c r="F50" s="87" t="n">
+        <v>28.13</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="87" t="n">
+        <v>20</v>
+      </c>
+      <c r="B51" s="87" t="n">
+        <v>62</v>
+      </c>
+      <c r="C51" s="87" t="n">
+        <v>56</v>
+      </c>
+      <c r="D51" s="87" t="n">
+        <v>73</v>
+      </c>
+      <c r="E51" s="88" t="n">
+        <v>0.000255</v>
+      </c>
+      <c r="F51" s="87" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="87" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="87" t="n">
+        <v>62</v>
+      </c>
+      <c r="C52" s="87" t="n">
+        <v>56</v>
+      </c>
+      <c r="D52" s="87" t="n">
+        <v>73</v>
+      </c>
+      <c r="E52" s="88" t="n">
+        <v>0.0002696</v>
+      </c>
+      <c r="F52" s="87" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="87" t="n">
+        <v>100</v>
+      </c>
+      <c r="B53" s="87" t="n">
+        <v>62</v>
+      </c>
+      <c r="C53" s="87" t="n">
+        <v>56</v>
+      </c>
+      <c r="D53" s="87" t="n">
+        <v>73</v>
+      </c>
+      <c r="E53" s="88" t="n">
+        <v>0.0002892</v>
+      </c>
+      <c r="F53" s="87" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="89" t="inlineStr">
+        <is>
+          <t>DP fine-tune = pretrained (trùng đường). Non-DP &amp; Paper là mốc tham chiếu (không phụ thuộc ε).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="33">
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A4:G4"/>
@@ -10078,6 +10592,7 @@
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A48:G48"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
@@ -10098,5 +10613,6 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/Federated_RAG_Privacy.xlsx
+++ b/docs/Federated_RAG_Privacy.xlsx
@@ -17,7 +17,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000E+00"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -196,6 +196,43 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00595959"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="15">
@@ -417,7 +454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -650,6 +687,43 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -727,7 +801,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -917,7 +990,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="3"/>
   <chart>
     <title>
       <tx>
@@ -9679,7 +9751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="49" min="1" max="1"/>
@@ -10367,8 +10439,8 @@
           <t>✅ ĐO THẬT: val H@1=62/MRR=48.47 · test H@1=62/MRR=47.03 = pretrained. σ=0.73 (nhiễu yếu nhất) VẪN không phá invariance → không có 'cliff' trong dải [1,100].</t>
         </is>
       </c>
-      <c r="F39" s="74" t="n"/>
-      <c r="G39" s="74" t="n"/>
+      <c r="F39" s="61" t="n"/>
+      <c r="G39" s="60" t="n"/>
     </row>
     <row r="40" ht="60" customHeight="1" s="49">
       <c r="A40" s="75" t="inlineStr">
@@ -10450,12 +10522,12 @@
           <t>10 · BIỂU ĐỒ PRIVACY–UTILITY (dữ liệu đo thật, paper-protocol + LlamaIndex)</t>
         </is>
       </c>
-      <c r="B48" s="54" t="n"/>
-      <c r="C48" s="54" t="n"/>
-      <c r="D48" s="54" t="n"/>
-      <c r="E48" s="54" t="n"/>
-      <c r="F48" s="54" t="n"/>
-      <c r="G48" s="54" t="n"/>
+      <c r="B48" s="61" t="n"/>
+      <c r="C48" s="61" t="n"/>
+      <c r="D48" s="61" t="n"/>
+      <c r="E48" s="61" t="n"/>
+      <c r="F48" s="61" t="n"/>
+      <c r="G48" s="60" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="86" t="inlineStr">
@@ -10576,8 +10648,319 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="56" t="inlineStr">
+        <is>
+          <t>11 · ABLATION STUDY (Khung 1) — loại bỏ từng thành phần recipe</t>
+        </is>
+      </c>
+      <c r="B56" s="54" t="n"/>
+      <c r="C56" s="54" t="n"/>
+      <c r="D56" s="54" t="n"/>
+      <c r="E56" s="54" t="n"/>
+      <c r="F56" s="54" t="n"/>
+      <c r="G56" s="54" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="90" t="inlineStr">
+        <is>
+          <t>Đo thật 2026-07-05 (Xeon Gold, paper-protocol+LI). Ma trận 2×2 DP×PEFT + ablation KD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="59" t="inlineStr">
+        <is>
+          <t>Val H@1 / Test H@1</t>
+        </is>
+      </c>
+      <c r="B58" s="59" t="inlineStr">
+        <is>
+          <t>LoRA (+PEFT)</t>
+        </is>
+      </c>
+      <c r="C58" s="59" t="inlineStr">
+        <is>
+          <t>full-FT (−PEFT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="91" t="inlineStr">
+        <is>
+          <t>+DP (ε=20)</t>
+        </is>
+      </c>
+      <c r="B59" s="73" t="inlineStr">
+        <is>
+          <t>62 / 62  (C)</t>
+        </is>
+      </c>
+      <c r="C59" s="73" t="inlineStr">
+        <is>
+          <t>60 / 60  (D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="91" t="inlineStr">
+        <is>
+          <t>−DP</t>
+        </is>
+      </c>
+      <c r="B60" s="77" t="inlineStr">
+        <is>
+          <t>58 / 56  (C'/B)</t>
+        </is>
+      </c>
+      <c r="C60" s="70" t="inlineStr">
+        <is>
+          <t>36 / 54  (D')</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="91" t="inlineStr">
+        <is>
+          <t>Pretrained</t>
+        </is>
+      </c>
+      <c r="B61" s="92" t="inlineStr">
+        <is>
+          <t>62 / 62</t>
+        </is>
+      </c>
+      <c r="C61" s="92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="86" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="B63" s="86" t="inlineStr">
+        <is>
+          <t>Recipe</t>
+        </is>
+      </c>
+      <c r="C63" s="86" t="inlineStr">
+        <is>
+          <t>Val H@1</t>
+        </is>
+      </c>
+      <c r="D63" s="86" t="inlineStr">
+        <is>
+          <t>Val MRR</t>
+        </is>
+      </c>
+      <c r="E63" s="86" t="inlineStr">
+        <is>
+          <t>Test H@1</t>
+        </is>
+      </c>
+      <c r="F63" s="86" t="inlineStr">
+        <is>
+          <t>Test MRR</t>
+        </is>
+      </c>
+      <c r="G63" s="86" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="93" t="inlineStr">
+        <is>
+          <t>Pretrained</t>
+        </is>
+      </c>
+      <c r="B64" s="94" t="inlineStr">
+        <is>
+          <t>BGE + LI (không train)</t>
+        </is>
+      </c>
+      <c r="C64" s="95" t="n">
+        <v>62</v>
+      </c>
+      <c r="D64" s="95" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="E64" s="95" t="n">
+        <v>62</v>
+      </c>
+      <c r="F64" s="95" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G64" s="94" t="inlineStr">
+        <is>
+          <t>mốc chuẩn</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="93" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B65" s="94" t="inlineStr">
+        <is>
+          <t>nonDP LoRA +KD</t>
+        </is>
+      </c>
+      <c r="C65" s="95" t="n">
+        <v>58</v>
+      </c>
+      <c r="D65" s="95" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="E65" s="95" t="n">
+        <v>56</v>
+      </c>
+      <c r="F65" s="95" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="G65" s="94" t="inlineStr">
+        <is>
+          <t>có sẵn (Run 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="93" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+      <c r="B66" s="94" t="inlineStr">
+        <is>
+          <t>nonDP LoRA −KD</t>
+        </is>
+      </c>
+      <c r="C66" s="95" t="n">
+        <v>58</v>
+      </c>
+      <c r="D66" s="95" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="E66" s="95" t="n">
+        <v>56</v>
+      </c>
+      <c r="F66" s="95" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="G66" s="94" t="inlineStr">
+        <is>
+          <t>≈ B → KD-GLE gần vô dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="96" t="inlineStr">
+        <is>
+          <t>D'</t>
+        </is>
+      </c>
+      <c r="B67" s="97" t="inlineStr">
+        <is>
+          <t>nonDP full-FT (−PEFT)</t>
+        </is>
+      </c>
+      <c r="C67" s="98" t="n">
+        <v>36</v>
+      </c>
+      <c r="D67" s="98" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="E67" s="98" t="n">
+        <v>54</v>
+      </c>
+      <c r="F67" s="98" t="n">
+        <v>39.62</v>
+      </c>
+      <c r="G67" s="97" t="inlineStr">
+        <is>
+          <t>⬇⬇ overfit nặng (val sập 36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="99" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B68" s="100" t="inlineStr">
+        <is>
+          <t>DP LoRA −KD</t>
+        </is>
+      </c>
+      <c r="C68" s="101" t="n">
+        <v>62</v>
+      </c>
+      <c r="D68" s="101" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="E68" s="101" t="n">
+        <v>62</v>
+      </c>
+      <c r="F68" s="101" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G68" s="100">
+        <f> pretrained (invariance)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="99" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B69" s="100" t="inlineStr">
+        <is>
+          <t>DP full-FT (−PEFT)</t>
+        </is>
+      </c>
+      <c r="C69" s="101" t="n">
+        <v>60</v>
+      </c>
+      <c r="D69" s="101" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="E69" s="101" t="n">
+        <v>60</v>
+      </c>
+      <c r="F69" s="101" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="G69" s="100" t="inlineStr">
+        <is>
+          <t>DP cứu full-FT: 36→60 (+24 val)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="64" customHeight="1" s="49">
+      <c r="A71" s="102" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN ABLATION: (1) DP là REGULARIZER mạnh — kéo cả LoRA (62) lẫn full-FT (60) về ≈ pretrained. (2) DP quan trọng NHẤT khi capacity cao: full-FT val 36→60 (+24) nhờ DP, vs LoRA 58→62 (+4). (3) PEFT (LoRA) tự nó cũng regularize: kể cả không DP, LoRA (58) ≫ full-FT (36). (4) KD-GLE gần như vô dụng (C'≈B). ⇒ Phổ ràng buộc: full-FT&lt;LoRA&lt;DP; càng ràng buộc càng giữ chất lượng.</t>
+        </is>
+      </c>
+      <c r="B71" s="54" t="n"/>
+      <c r="C71" s="54" t="n"/>
+      <c r="D71" s="54" t="n"/>
+      <c r="E71" s="54" t="n"/>
+      <c r="F71" s="54" t="n"/>
+      <c r="G71" s="54" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="36">
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="A8:G8"/>
@@ -10605,11 +10988,14 @@
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A56:G56"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E35:G35"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A71:G71"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/Federated_RAG_Privacy.xlsx
+++ b/docs/Federated_RAG_Privacy.xlsx
@@ -17,7 +17,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000E+00"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -232,6 +232,17 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00595959"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -454,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -723,6 +734,21 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9751,7 +9777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="49" min="1" max="1"/>
@@ -10654,12 +10680,12 @@
           <t>11 · ABLATION STUDY (Khung 1) — loại bỏ từng thành phần recipe</t>
         </is>
       </c>
-      <c r="B56" s="54" t="n"/>
-      <c r="C56" s="54" t="n"/>
-      <c r="D56" s="54" t="n"/>
-      <c r="E56" s="54" t="n"/>
-      <c r="F56" s="54" t="n"/>
-      <c r="G56" s="54" t="n"/>
+      <c r="B56" s="61" t="n"/>
+      <c r="C56" s="61" t="n"/>
+      <c r="D56" s="61" t="n"/>
+      <c r="E56" s="61" t="n"/>
+      <c r="F56" s="61" t="n"/>
+      <c r="G56" s="60" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="90" t="inlineStr">
@@ -10952,18 +10978,348 @@
           <t>KẾT LUẬN ABLATION: (1) DP là REGULARIZER mạnh — kéo cả LoRA (62) lẫn full-FT (60) về ≈ pretrained. (2) DP quan trọng NHẤT khi capacity cao: full-FT val 36→60 (+24) nhờ DP, vs LoRA 58→62 (+4). (3) PEFT (LoRA) tự nó cũng regularize: kể cả không DP, LoRA (58) ≫ full-FT (36). (4) KD-GLE gần như vô dụng (C'≈B). ⇒ Phổ ràng buộc: full-FT&lt;LoRA&lt;DP; càng ràng buộc càng giữ chất lượng.</t>
         </is>
       </c>
-      <c r="B71" s="54" t="n"/>
-      <c r="C71" s="54" t="n"/>
-      <c r="D71" s="54" t="n"/>
-      <c r="E71" s="54" t="n"/>
-      <c r="F71" s="54" t="n"/>
-      <c r="G71" s="54" t="n"/>
+      <c r="B71" s="61" t="n"/>
+      <c r="C71" s="61" t="n"/>
+      <c r="D71" s="61" t="n"/>
+      <c r="E71" s="61" t="n"/>
+      <c r="F71" s="61" t="n"/>
+      <c r="G71" s="60" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="56" t="inlineStr">
+        <is>
+          <t>12 · BỘ CHỈ SỐ ĐẦY ĐỦ (parity với paper) — TEST split, đo thật 2026-07-06</t>
+        </is>
+      </c>
+      <c r="B73" s="54" t="n"/>
+      <c r="C73" s="54" t="n"/>
+      <c r="D73" s="54" t="n"/>
+      <c r="E73" s="54" t="n"/>
+      <c r="F73" s="54" t="n"/>
+      <c r="G73" s="54" t="n"/>
+      <c r="H73" s="54" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="90" t="inlineStr">
+        <is>
+          <t>Hit@1/3/5/10 (paper def) · MRR · MAP · NDCG@10 · EM · Recall/Precision@{1,5,10}. Lưu ý: Hit@3=Hit@5=Hit@10 (do def paper + đa số query ≤3 golden) → dùng NDCG/MAP/Recall để phân biệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="86" t="inlineStr">
+        <is>
+          <t>Config (test n=100)</t>
+        </is>
+      </c>
+      <c r="B75" s="86" t="inlineStr">
+        <is>
+          <t>Hit@1</t>
+        </is>
+      </c>
+      <c r="C75" s="86" t="inlineStr">
+        <is>
+          <t>Hit@10</t>
+        </is>
+      </c>
+      <c r="D75" s="86" t="inlineStr">
+        <is>
+          <t>MRR</t>
+        </is>
+      </c>
+      <c r="E75" s="86" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="F75" s="86" t="inlineStr">
+        <is>
+          <t>NDCG@10</t>
+        </is>
+      </c>
+      <c r="G75" s="86" t="inlineStr">
+        <is>
+          <t>Recall@10</t>
+        </is>
+      </c>
+      <c r="H75" s="86" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="103" t="inlineStr">
+        <is>
+          <t>Pretrained</t>
+        </is>
+      </c>
+      <c r="B76" s="104" t="n">
+        <v>62</v>
+      </c>
+      <c r="C76" s="104" t="n">
+        <v>71</v>
+      </c>
+      <c r="D76" s="104" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E76" s="104" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="F76" s="104" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="G76" s="104" t="n">
+        <v>66</v>
+      </c>
+      <c r="H76" s="104" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="105" t="inlineStr">
+        <is>
+          <t>DP ε=1</t>
+        </is>
+      </c>
+      <c r="B77" s="95" t="n">
+        <v>62</v>
+      </c>
+      <c r="C77" s="95" t="n">
+        <v>71</v>
+      </c>
+      <c r="D77" s="95" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E77" s="95" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="F77" s="95" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="G77" s="95" t="n">
+        <v>66</v>
+      </c>
+      <c r="H77" s="95" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="105" t="inlineStr">
+        <is>
+          <t>DP ε=20</t>
+        </is>
+      </c>
+      <c r="B78" s="95" t="n">
+        <v>62</v>
+      </c>
+      <c r="C78" s="95" t="n">
+        <v>71</v>
+      </c>
+      <c r="D78" s="95" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E78" s="95" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="F78" s="95" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="G78" s="95" t="n">
+        <v>66</v>
+      </c>
+      <c r="H78" s="95" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="105" t="inlineStr">
+        <is>
+          <t>DP ε=50</t>
+        </is>
+      </c>
+      <c r="B79" s="95" t="n">
+        <v>62</v>
+      </c>
+      <c r="C79" s="95" t="n">
+        <v>71</v>
+      </c>
+      <c r="D79" s="95" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="E79" s="95" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="F79" s="95" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="G79" s="95" t="n">
+        <v>66</v>
+      </c>
+      <c r="H79" s="95" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="106" t="inlineStr">
+        <is>
+          <t>DP ε=100</t>
+        </is>
+      </c>
+      <c r="B80" s="101" t="n">
+        <v>62</v>
+      </c>
+      <c r="C80" s="101" t="n">
+        <v>71</v>
+      </c>
+      <c r="D80" s="101" t="n">
+        <v>47.03</v>
+      </c>
+      <c r="E80" s="101" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F80" s="101" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="G80" s="101" t="n">
+        <v>66</v>
+      </c>
+      <c r="H80" s="101" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="105" t="inlineStr">
+        <is>
+          <t>Abl: nonDP LoRA −KD</t>
+        </is>
+      </c>
+      <c r="B81" s="95" t="n">
+        <v>56</v>
+      </c>
+      <c r="C81" s="95" t="n">
+        <v>66</v>
+      </c>
+      <c r="D81" s="95" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="E81" s="95" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F81" s="95" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="G81" s="95" t="n">
+        <v>61</v>
+      </c>
+      <c r="H81" s="95" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="107" t="inlineStr">
+        <is>
+          <t>Abl: nonDP full-FT</t>
+        </is>
+      </c>
+      <c r="B82" s="98" t="n">
+        <v>54</v>
+      </c>
+      <c r="C82" s="98" t="n">
+        <v>59</v>
+      </c>
+      <c r="D82" s="98" t="n">
+        <v>39.62</v>
+      </c>
+      <c r="E82" s="98" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="F82" s="98" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="G82" s="98" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="H82" s="98" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="106" t="inlineStr">
+        <is>
+          <t>Abl: DP LoRA −KD</t>
+        </is>
+      </c>
+      <c r="B83" s="101" t="n">
+        <v>62</v>
+      </c>
+      <c r="C83" s="101" t="n">
+        <v>71</v>
+      </c>
+      <c r="D83" s="101" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E83" s="101" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="F83" s="101" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="G83" s="101" t="n">
+        <v>66</v>
+      </c>
+      <c r="H83" s="101" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="106" t="inlineStr">
+        <is>
+          <t>Abl: DP full-FT</t>
+        </is>
+      </c>
+      <c r="B84" s="101" t="n">
+        <v>60</v>
+      </c>
+      <c r="C84" s="101" t="n">
+        <v>70</v>
+      </c>
+      <c r="D84" s="101" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="E84" s="101" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="F84" s="101" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="G84" s="101" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="H84" s="101" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86" ht="64" customHeight="1" s="49">
+      <c r="A86" s="102" t="inlineStr">
+        <is>
+          <t>★ PHÁT HIỆN (trả lời 'đánh giá thiếu giá trị'): DP full-FT có Hit@1=60 (&lt; pretrained 62) TRÔNG như kém hơn, NHƯNG trên VAL nó MRR=49.97 / NDCG=50.17 / MAP=45.22 / Recall@1=35 / Precision@1=42 — ĐỀU CAO HƠN pretrained (48.47/49.10/43.80/33/40). ⇒ Chỉ nhìn Hit@1 đã ĐÁNH GIÁ THẤP method; NDCG/MAP/MRR mới lộ đúng giá trị. Non-DP full-FT thì sập ĐỒNG LOẠT mọi chỉ số (NDCG 29, MAP 25 trên val) — xác nhận overfit.</t>
+        </is>
+      </c>
+      <c r="B86" s="54" t="n"/>
+      <c r="C86" s="54" t="n"/>
+      <c r="D86" s="54" t="n"/>
+      <c r="E86" s="54" t="n"/>
+      <c r="F86" s="54" t="n"/>
+      <c r="G86" s="54" t="n"/>
+      <c r="H86" s="54" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="39">
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="A42:G42"/>
@@ -10981,8 +11337,10 @@
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A74:H74"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E38:G38"/>
+    <mergeCell ref="A86:H86"/>
     <mergeCell ref="E37:G37"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A46:G46"/>
